--- a/astro-site/public/dl/bar-checklist-templates/05-bar-cleaning-checklist-inventory-maintenance.xlsx
+++ b/astro-site/public/dl/bar-checklist-templates/05-bar-cleaning-checklist-inventory-maintenance.xlsx
@@ -2804,7 +2804,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Freezer time</t>
+          <t>Shelf life</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -2872,14 +2872,14 @@
       </c>
       <c r="D39" s="40" t="inlineStr">
         <is>
-          <t>Label with the prep date; orgeat contains ALMOND (tree nut) and must be declared on the menu</t>
+          <t>Label with the prep date; orgeat contains ALMOND (tree nut): list it on the menu or your written allergen sheet</t>
         </is>
       </c>
       <c r="E39" s="35" t="n"/>
       <c r="F39" s="35" t="n"/>
       <c r="G39" s="36" t="n"/>
     </row>
-    <row r="40" ht="30" customHeight="1">
+    <row r="40" ht="45" customHeight="1">
       <c r="A40" s="30" t="n"/>
       <c r="B40" s="45" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="D40" s="40" t="inlineStr">
         <is>
-          <t>Spirits and fortified wines only: capped bottle, refrigerated, away from light</t>
+          <t>Spirits and fortified wines only: sealed, labeled container (never back into an empty liquor bottle), refrigerated, away from light</t>
         </is>
       </c>
       <c r="E40" s="35" t="n"/>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="D44" s="40" t="inlineStr">
         <is>
-          <t>Keg date rules (Brewers Association: 45–60 days unpasteurized, 90–120 days pasteurized, from packaging) with a balanced system and lines cleaned every 2 weeks; the old "3–5 days" rule only applies to air pumps (party pumps)</t>
+          <t>Keg date rules (Brewers Association: 45–60 days unpasteurized, 90–120 days pasteurized, from packaging) with a balanced CO₂ system and lines cleaned every 2 weeks; on an air pump (party pump), finish the keg the same day</t>
         </is>
       </c>
       <c r="E44" s="35" t="n"/>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="B14" s="38" t="inlineStr">
         <is>
-          <t>Replace the water filter on the ice machine and the espresso machine, and test water hardness to set the descaling frequency</t>
+          <t>Ice machine: clean and sanitize the bin and evaporator per the manufacturer (check for mold and slime); replace its water filter and the espresso machine's, and test water hardness to set the descaling frequency</t>
         </is>
       </c>
       <c r="C14" s="39" t="n"/>
